--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21847,7 +21847,7 @@
         <v>121076904</v>
       </c>
       <c r="B178" t="n">
-        <v>57375</v>
+        <v>57376</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21847,7 +21847,7 @@
         <v>121076904</v>
       </c>
       <c r="B178" t="n">
-        <v>57376</v>
+        <v>57377</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY175"/>
+  <dimension ref="A1:AY180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21595,6 +21595,566 @@
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>122895421</v>
+      </c>
+      <c r="B176" t="n">
+        <v>94866</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Neckera pennata</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>628079</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6705795</v>
+      </c>
+      <c r="S176" t="n">
+        <v>25</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>122895427</v>
+      </c>
+      <c r="B177" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>628085</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6705790</v>
+      </c>
+      <c r="S177" t="n">
+        <v>25</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>122895461</v>
+      </c>
+      <c r="B178" t="n">
+        <v>94866</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Neckera pennata</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>628006</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6705651</v>
+      </c>
+      <c r="S178" t="n">
+        <v>25</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>122895467</v>
+      </c>
+      <c r="B179" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>628006</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6705651</v>
+      </c>
+      <c r="S179" t="n">
+        <v>25</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>122895471</v>
+      </c>
+      <c r="B180" t="n">
+        <v>82409</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>779</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Lindskål</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Holwaya mucida</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Schulzer) Korf &amp; Abawi</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>628006</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6705651</v>
+      </c>
+      <c r="S180" t="n">
+        <v>25</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895421</v>
+        <v>122895467</v>
       </c>
       <c r="B176" t="n">
-        <v>94866</v>
+        <v>79847</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21637,10 +21637,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>628079</v>
+        <v>628006</v>
       </c>
       <c r="R176" t="n">
-        <v>6705795</v>
+        <v>6705651</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895467</v>
+        <v>122895421</v>
       </c>
       <c r="B179" t="n">
-        <v>79847</v>
+        <v>94866</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628006</v>
+        <v>628079</v>
       </c>
       <c r="R179" t="n">
-        <v>6705651</v>
+        <v>6705795</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895421</v>
+        <v>122895471</v>
       </c>
       <c r="B179" t="n">
-        <v>94866</v>
+        <v>82409</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1079</v>
+        <v>779</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628079</v>
+        <v>628006</v>
       </c>
       <c r="R179" t="n">
-        <v>6705795</v>
+        <v>6705651</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22045,10 +22045,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122895471</v>
+        <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>82409</v>
+        <v>94866</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -22057,25 +22057,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>779</v>
+        <v>1079</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628006</v>
+        <v>628079</v>
       </c>
       <c r="R180" t="n">
-        <v>6705651</v>
+        <v>6705795</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895467</v>
+        <v>122895427</v>
       </c>
       <c r="B176" t="n">
-        <v>79847</v>
+        <v>79892</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21613,21 +21613,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>229504</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21637,10 +21637,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R176" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -21702,17 +21702,17 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895427</v>
+        <v>122895461</v>
       </c>
       <c r="B177" t="n">
-        <v>79892</v>
+        <v>94866</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21721,25 +21721,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229504</v>
+        <v>1079</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -21749,10 +21749,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R177" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -21814,14 +21814,14 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895461</v>
+        <v>122895421</v>
       </c>
       <c r="B178" t="n">
         <v>94866</v>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628006</v>
+        <v>628079</v>
       </c>
       <c r="R178" t="n">
-        <v>6705651</v>
+        <v>6705795</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21926,17 +21926,17 @@
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895471</v>
+        <v>122895467</v>
       </c>
       <c r="B179" t="n">
-        <v>82409</v>
+        <v>79847</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>779</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -22038,17 +22038,17 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122895421</v>
+        <v>122895471</v>
       </c>
       <c r="B180" t="n">
-        <v>94866</v>
+        <v>82409</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -22057,25 +22057,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1079</v>
+        <v>779</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628079</v>
+        <v>628006</v>
       </c>
       <c r="R180" t="n">
-        <v>6705795</v>
+        <v>6705651</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895427</v>
+        <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>79892</v>
+        <v>94866</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229504</v>
+        <v>1079</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21637,10 +21637,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R176" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -21709,10 +21709,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895461</v>
+        <v>122895467</v>
       </c>
       <c r="B177" t="n">
-        <v>94866</v>
+        <v>79847</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21721,25 +21721,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895421</v>
+        <v>122895471</v>
       </c>
       <c r="B178" t="n">
-        <v>94866</v>
+        <v>82409</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1079</v>
+        <v>779</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628079</v>
+        <v>628006</v>
       </c>
       <c r="R178" t="n">
-        <v>6705795</v>
+        <v>6705651</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895467</v>
+        <v>122895421</v>
       </c>
       <c r="B179" t="n">
-        <v>79847</v>
+        <v>94866</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628006</v>
+        <v>628079</v>
       </c>
       <c r="R179" t="n">
-        <v>6705651</v>
+        <v>6705795</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22045,10 +22045,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122895471</v>
+        <v>122895427</v>
       </c>
       <c r="B180" t="n">
-        <v>82409</v>
+        <v>79892</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -22057,25 +22057,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>779</v>
+        <v>229504</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R180" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895421</v>
+        <v>122895427</v>
       </c>
       <c r="B179" t="n">
-        <v>94866</v>
+        <v>79892</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1079</v>
+        <v>229504</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628079</v>
+        <v>628085</v>
       </c>
       <c r="R179" t="n">
-        <v>6705795</v>
+        <v>6705790</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22045,37 +22045,37 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122895427</v>
+        <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>79892</v>
+        <v>94866</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229504</v>
+        <v>1079</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -22085,10 +22085,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628085</v>
+        <v>628079</v>
       </c>
       <c r="R180" t="n">
-        <v>6705790</v>
+        <v>6705795</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21600,7 +21600,7 @@
         <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>94866</v>
+        <v>94874</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21709,10 +21709,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895467</v>
+        <v>122895427</v>
       </c>
       <c r="B177" t="n">
-        <v>79847</v>
+        <v>79892</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21725,21 +21725,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>229504</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -21749,10 +21749,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R177" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895427</v>
+        <v>122895467</v>
       </c>
       <c r="B179" t="n">
-        <v>79892</v>
+        <v>79847</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21949,21 +21949,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R179" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94866</v>
+        <v>94874</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895461</v>
+        <v>122895467</v>
       </c>
       <c r="B176" t="n">
-        <v>94874</v>
+        <v>79847</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895471</v>
+        <v>122895461</v>
       </c>
       <c r="B178" t="n">
-        <v>82409</v>
+        <v>94874</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>779</v>
+        <v>1079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895467</v>
+        <v>122895471</v>
       </c>
       <c r="B179" t="n">
-        <v>79847</v>
+        <v>82409</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>779</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21709,10 +21709,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895427</v>
+        <v>122895471</v>
       </c>
       <c r="B177" t="n">
-        <v>79892</v>
+        <v>82409</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21721,25 +21721,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229504</v>
+        <v>779</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -21749,10 +21749,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R177" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895471</v>
+        <v>122895427</v>
       </c>
       <c r="B179" t="n">
-        <v>82409</v>
+        <v>79892</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>779</v>
+        <v>229504</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R179" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895467</v>
+        <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>79847</v>
+        <v>94874</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895461</v>
+        <v>122895467</v>
       </c>
       <c r="B178" t="n">
-        <v>94874</v>
+        <v>79847</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21600,7 +21600,7 @@
         <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>94874</v>
+        <v>94877</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21709,10 +21709,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895471</v>
+        <v>122895467</v>
       </c>
       <c r="B177" t="n">
-        <v>82409</v>
+        <v>79850</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21721,25 +21721,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>779</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895467</v>
+        <v>122895427</v>
       </c>
       <c r="B178" t="n">
-        <v>79847</v>
+        <v>79895</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21837,21 +21837,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>229504</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R178" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895427</v>
+        <v>122895471</v>
       </c>
       <c r="B179" t="n">
-        <v>79892</v>
+        <v>82412</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229504</v>
+        <v>779</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R179" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94874</v>
+        <v>94877</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895461</v>
+        <v>122895471</v>
       </c>
       <c r="B176" t="n">
-        <v>94877</v>
+        <v>82414</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1079</v>
+        <v>779</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21712,7 +21712,7 @@
         <v>122895467</v>
       </c>
       <c r="B177" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895427</v>
+        <v>122895461</v>
       </c>
       <c r="B178" t="n">
-        <v>79895</v>
+        <v>94879</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229504</v>
+        <v>1079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R178" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895471</v>
+        <v>122895427</v>
       </c>
       <c r="B179" t="n">
-        <v>82412</v>
+        <v>79897</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>779</v>
+        <v>229504</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R179" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94877</v>
+        <v>94879</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895471</v>
+        <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>82414</v>
+        <v>94885</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>779</v>
+        <v>1079</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21712,7 +21712,7 @@
         <v>122895467</v>
       </c>
       <c r="B177" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895461</v>
+        <v>122895427</v>
       </c>
       <c r="B178" t="n">
-        <v>94879</v>
+        <v>79898</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1079</v>
+        <v>229504</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628006</v>
+        <v>628085</v>
       </c>
       <c r="R178" t="n">
-        <v>6705651</v>
+        <v>6705790</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -21933,10 +21933,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895427</v>
+        <v>122895471</v>
       </c>
       <c r="B179" t="n">
-        <v>79897</v>
+        <v>82415</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21945,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229504</v>
+        <v>779</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +21973,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R179" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94879</v>
+        <v>94885</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -21597,10 +21597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895467</v>
+        <v>122895461</v>
       </c>
       <c r="B176" t="n">
-        <v>79856</v>
+        <v>94905</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,25 +21609,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -21712,7 +21712,7 @@
         <v>122895471</v>
       </c>
       <c r="B177" t="n">
-        <v>82418</v>
+        <v>82424</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21821,10 +21821,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895461</v>
+        <v>122895467</v>
       </c>
       <c r="B178" t="n">
-        <v>94888</v>
+        <v>79862</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,25 +21833,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -21936,7 +21936,7 @@
         <v>122895427</v>
       </c>
       <c r="B179" t="n">
-        <v>79901</v>
+        <v>79907</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94888</v>
+        <v>94905</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94905</v>
+        <v>94911</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -22048,7 +22048,7 @@
         <v>122895421</v>
       </c>
       <c r="B180" t="n">
-        <v>94911</v>
+        <v>94913</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY180"/>
+  <dimension ref="A1:AY183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12020,10 +12020,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>62000859</v>
+        <v>62000395</v>
       </c>
       <c r="B96" t="n">
-        <v>98008</v>
+        <v>95511</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12032,35 +12032,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1256</v>
+        <v>221944</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628830.0394527031</v>
+        <v>628271.1002280297</v>
       </c>
       <c r="R96" t="n">
-        <v>6706445.009445602</v>
+        <v>6706205.047771081</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
@@ -12141,10 +12141,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>64526644</v>
+        <v>62000859</v>
       </c>
       <c r="B97" t="n">
-        <v>55893</v>
+        <v>98008</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12157,49 +12157,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>206004</v>
+        <v>1256</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vändplats, Väg mot Skrammelön, Båtforsområdet, Upl</t>
+          <t>Storön (utanför Båtfors NR), Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628243</v>
+        <v>628830.0394527031</v>
       </c>
       <c r="R97" t="n">
-        <v>6706211</v>
+        <v>6706445.009445602</v>
       </c>
       <c r="S97" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12223,12 +12220,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2017-03-20</t>
+          <t>2016-06-05</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2017-03-20</t>
+          <t>2016-06-05</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12243,22 +12250,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ante Strand</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ante Strand</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>67220689</v>
+        <v>64526644</v>
       </c>
       <c r="B98" t="n">
-        <v>100515</v>
+        <v>55893</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12267,44 +12274,53 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223246</v>
+        <v>206004</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Storön, N om Mellanön, Upl</t>
+          <t>Vändplats, Väg mot Skrammelön, Båtforsområdet, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628234.4205795483</v>
+        <v>628243</v>
       </c>
       <c r="R98" t="n">
-        <v>6706082.341267481</v>
+        <v>6706211</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12328,22 +12344,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2017-03-20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12358,22 +12364,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Ante Strand</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+          <t>Ante Strand</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>67220682</v>
+        <v>67220689</v>
       </c>
       <c r="B99" t="n">
-        <v>98520</v>
+        <v>100515</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12382,25 +12388,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>223246</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12485,10 +12491,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>67220331</v>
+        <v>67220682</v>
       </c>
       <c r="B100" t="n">
-        <v>73699</v>
+        <v>98520</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12497,30 +12503,31 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1468</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brunskaftad blekspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sclerophora farinacea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Chevall.) Chevall.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Storön, N om Mellanön, Upl</t>
@@ -12583,21 +12590,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12614,10 +12606,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>67219748</v>
+        <v>67220331</v>
       </c>
       <c r="B101" t="n">
-        <v>101680</v>
+        <v>73699</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12626,41 +12618,40 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222412</v>
+        <v>1468</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brunskaftad blekspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sclerophora farinacea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Chevall.) Chevall.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628244.7452740758</v>
+        <v>628234.4205795483</v>
       </c>
       <c r="R101" t="n">
-        <v>6706111.82534453</v>
+        <v>6706082.341267481</v>
       </c>
       <c r="S101" t="n">
         <v>50</v>
@@ -12713,6 +12704,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12729,10 +12735,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>67235984</v>
+        <v>67219748</v>
       </c>
       <c r="B102" t="n">
-        <v>98431</v>
+        <v>101680</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12745,16 +12751,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -12762,35 +12768,23 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Storön, Upl</t>
+          <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628219.0757804178</v>
+        <v>628244.7452740758</v>
       </c>
       <c r="R102" t="n">
-        <v>6706068.96565874</v>
+        <v>6706111.82534453</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12819,7 +12813,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12829,7 +12823,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12844,19 +12838,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>67220271</v>
+        <v>67235984</v>
       </c>
       <c r="B103" t="n">
         <v>98431</v>
@@ -12889,8 +12883,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -12899,17 +12901,17 @@
       <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Storön, N om Mellanön, Upl</t>
+          <t>Storön, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628234.4205795483</v>
+        <v>628219.0757804178</v>
       </c>
       <c r="R103" t="n">
-        <v>6706082.341267481</v>
+        <v>6706068.96565874</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12938,7 +12940,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12948,7 +12950,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12963,22 +12965,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>67219785</v>
+        <v>67220271</v>
       </c>
       <c r="B104" t="n">
-        <v>103346</v>
+        <v>98431</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12991,26 +12993,30 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221423</v>
+        <v>222771</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13018,10 +13024,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628244.7452740758</v>
+        <v>628234.4205795483</v>
       </c>
       <c r="R104" t="n">
-        <v>6706111.82534453</v>
+        <v>6706082.341267481</v>
       </c>
       <c r="S104" t="n">
         <v>50</v>
@@ -13090,10 +13096,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>67219701</v>
+        <v>67219785</v>
       </c>
       <c r="B105" t="n">
-        <v>103088</v>
+        <v>103346</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13106,30 +13112,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221101</v>
+        <v>221423</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13137,13 +13139,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628241.7965730567</v>
+        <v>628244.7452740758</v>
       </c>
       <c r="R105" t="n">
-        <v>6706153.176750403</v>
+        <v>6706111.82534453</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13202,17 +13204,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>67219760</v>
+        <v>67219701</v>
       </c>
       <c r="B106" t="n">
-        <v>98008</v>
+        <v>103088</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13221,30 +13223,34 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1256</v>
+        <v>221101</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -13252,13 +13258,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628244.7452740758</v>
+        <v>628241.7965730567</v>
       </c>
       <c r="R106" t="n">
-        <v>6706111.82534453</v>
+        <v>6706153.176750403</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13317,17 +13323,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson, Karin Wiklund</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>67219708</v>
+        <v>67219760</v>
       </c>
       <c r="B107" t="n">
-        <v>103813</v>
+        <v>98008</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13336,25 +13342,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220785</v>
+        <v>1256</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13367,13 +13373,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628241.7965730567</v>
+        <v>628244.7452740758</v>
       </c>
       <c r="R107" t="n">
-        <v>6706153.176750403</v>
+        <v>6706111.82534453</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13432,17 +13438,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>67220286</v>
+        <v>67219708</v>
       </c>
       <c r="B108" t="n">
-        <v>101120</v>
+        <v>103813</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13451,20 +13457,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222002</v>
+        <v>220785</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -13482,13 +13488,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628234.4205795483</v>
+        <v>628241.7965730567</v>
       </c>
       <c r="R108" t="n">
-        <v>6706082.341267481</v>
+        <v>6706153.176750403</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13554,10 +13560,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>67220241</v>
+        <v>67220286</v>
       </c>
       <c r="B109" t="n">
-        <v>101323</v>
+        <v>101120</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13570,16 +13576,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222395</v>
+        <v>222002</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -13662,17 +13668,17 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Wiklund</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>67220750</v>
+        <v>67220241</v>
       </c>
       <c r="B110" t="n">
-        <v>97655</v>
+        <v>101323</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13681,25 +13687,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>643</v>
+        <v>222395</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13712,13 +13718,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>628227.8762544694</v>
+        <v>628234.4205795483</v>
       </c>
       <c r="R110" t="n">
-        <v>6706127.513764501</v>
+        <v>6706082.341267481</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13777,17 +13783,17 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson, Karin Wiklund</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>67258346</v>
+        <v>67220750</v>
       </c>
       <c r="B111" t="n">
-        <v>84577</v>
+        <v>97655</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13796,51 +13802,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>505</v>
+        <v>643</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Flockig puderskivling</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystolepiota adulterina</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(F.H.Møller) Bon</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pollich) Holub</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628244.7452740758</v>
+        <v>628227.8762544694</v>
       </c>
       <c r="R111" t="n">
-        <v>6706111.82534453</v>
+        <v>6706127.513764501</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13882,18 +13881,12 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Bestämd av Karin Martinsson.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -13912,14 +13905,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>67251433</v>
+        <v>67258346</v>
       </c>
       <c r="B112" t="n">
-        <v>85415</v>
+        <v>84577</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13947,12 +13940,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -13962,10 +13955,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628245</v>
+        <v>628244.7452740758</v>
       </c>
       <c r="R112" t="n">
-        <v>6706119</v>
+        <v>6706111.82534453</v>
       </c>
       <c r="S112" t="n">
         <v>50</v>
@@ -13995,9 +13988,24 @@
           <t>2017-08-20</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2017-08-20</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Bestämd av Karin Martinsson.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14013,59 +14021,59 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Åke Berg, Niklas Hjort, Owe Rosengren, Patrick Fritzson</t>
+          <t>Owe Rosengren, Åke Berg, Niklas Hjort, Patrick Fritzson, Karin Martinsson, Karin Wiklund</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>67261281</v>
+        <v>67251433</v>
       </c>
       <c r="B113" t="n">
-        <v>84584</v>
+        <v>85415</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>239098</v>
+        <v>505</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blek puderskivling</t>
+          <t>Flockig puderskivling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cystolepiota seminuda</t>
+          <t>Cystolepiota adulterina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Lasch) Bon</t>
+          <t>(F.H.Møller) Bon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -14075,10 +14083,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628245.5055732524</v>
+        <v>628245</v>
       </c>
       <c r="R113" t="n">
-        <v>6706118.268122346</v>
+        <v>6706119</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -14108,24 +14116,9 @@
           <t>2017-08-20</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2017-08-20</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Exkursion med Upplands botaniska förening.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14138,30 +14131,25 @@
       <c r="AG113" t="b">
         <v>0</v>
       </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Karin Martinsson, Åke Berg, Niklas Hjort, Owe Rosengren, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>67980303</v>
+        <v>67261281</v>
       </c>
       <c r="B114" t="n">
-        <v>103346</v>
+        <v>84584</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14174,46 +14162,47 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221423</v>
+        <v>239098</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Blek puderskivling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cystolepiota seminuda</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Lasch) Bon</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>627952.1795003244</v>
+        <v>628245.5055732524</v>
       </c>
       <c r="R114" t="n">
-        <v>6705788.065971456</v>
+        <v>6706118.268122346</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14222,7 +14211,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -14232,12 +14221,12 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2016-11-27</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
@@ -14247,7 +14236,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2016-11-27</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
@@ -14255,34 +14244,45 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Exkursion med Upplands botaniska förening.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>67980085</v>
+        <v>67980303</v>
       </c>
       <c r="B115" t="n">
-        <v>98008</v>
+        <v>103346</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14291,38 +14291,47 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1256</v>
+        <v>221423</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Forselles</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>627999.2525125929</v>
+        <v>627952.1795003244</v>
       </c>
       <c r="R115" t="n">
-        <v>6705896.83317604</v>
+        <v>6705788.065971456</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14349,7 +14358,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2017-08-27</t>
+          <t>2016-11-27</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
@@ -14359,17 +14368,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2017-08-27</t>
+          <t>2016-11-27</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>spridd</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14396,10 +14400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>67980562</v>
+        <v>67980085</v>
       </c>
       <c r="B116" t="n">
-        <v>101323</v>
+        <v>98008</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14408,47 +14412,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222395</v>
+        <v>1256</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628132.171013276</v>
+        <v>627999.2525125929</v>
       </c>
       <c r="R116" t="n">
-        <v>6706135.967682488</v>
+        <v>6705896.83317604</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14460,7 +14455,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -14470,12 +14465,12 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-08-27</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
@@ -14485,12 +14480,17 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-08-27</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>spridd</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14517,10 +14517,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>67980098</v>
+        <v>67980562</v>
       </c>
       <c r="B117" t="n">
-        <v>103088</v>
+        <v>101323</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221101</v>
+        <v>222395</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14566,10 +14566,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628283.9670817981</v>
+        <v>628132.171013276</v>
       </c>
       <c r="R117" t="n">
-        <v>6706134.930864995</v>
+        <v>6706135.967682488</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>67980100</v>
+        <v>67980098</v>
       </c>
       <c r="B118" t="n">
         <v>103088</v>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628263.0342574168</v>
+        <v>628283.9670817981</v>
       </c>
       <c r="R118" t="n">
-        <v>6706070.030181158</v>
+        <v>6706134.930864995</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14759,10 +14759,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>67980038</v>
+        <v>67980100</v>
       </c>
       <c r="B119" t="n">
-        <v>98431</v>
+        <v>103088</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14775,16 +14775,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -14808,10 +14808,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628204.8954110144</v>
+        <v>628263.0342574168</v>
       </c>
       <c r="R119" t="n">
-        <v>6706162.232877192</v>
+        <v>6706070.030181158</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
@@ -14848,17 +14848,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>finaste örtmark, sek unggranskog m björk ädellövinslag</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14885,10 +14880,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>67980995</v>
+        <v>67980038</v>
       </c>
       <c r="B120" t="n">
-        <v>88953</v>
+        <v>98431</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14897,38 +14892,47 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628101.2513586337</v>
+        <v>628204.8954110144</v>
       </c>
       <c r="R120" t="n">
-        <v>6706059.85684723</v>
+        <v>6706162.232877192</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14955,7 +14959,7 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
@@ -14965,7 +14969,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -14975,7 +14979,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>lokalt rikligt</t>
+          <t>finaste örtmark, sek unggranskog m björk ädellövinslag</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15002,10 +15006,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>67980086</v>
+        <v>67980995</v>
       </c>
       <c r="B121" t="n">
-        <v>98008</v>
+        <v>88953</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15018,21 +15022,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1256</v>
+        <v>5754</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -15042,10 +15046,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628283.0102438813</v>
+        <v>628101.2513586337</v>
       </c>
       <c r="R121" t="n">
-        <v>6706120.091218494</v>
+        <v>6706059.85684723</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15072,7 +15076,7 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
@@ -15082,7 +15086,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -15092,7 +15096,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>lokalt rikligt</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15119,10 +15123,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>67980101</v>
+        <v>67980086</v>
       </c>
       <c r="B122" t="n">
-        <v>103088</v>
+        <v>98008</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15131,47 +15135,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221101</v>
+        <v>1256</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628109.2348518081</v>
+        <v>628283.0102438813</v>
       </c>
       <c r="R122" t="n">
-        <v>6705904.18031231</v>
+        <v>6706120.091218494</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15183,7 +15178,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -15193,7 +15188,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -15214,6 +15209,11 @@
       <c r="AB122" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15240,10 +15240,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>67980245</v>
+        <v>67980101</v>
       </c>
       <c r="B123" t="n">
-        <v>100515</v>
+        <v>103088</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15252,25 +15252,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>223246</v>
+        <v>221101</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15289,10 +15289,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>627930.8491470228</v>
+        <v>628109.2348518081</v>
       </c>
       <c r="R123" t="n">
-        <v>6705804.092998104</v>
+        <v>6705904.18031231</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2017-09-24</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
@@ -15329,17 +15329,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2017-09-24</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>3 dm</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15366,10 +15361,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>67979969</v>
+        <v>67980245</v>
       </c>
       <c r="B124" t="n">
-        <v>98431</v>
+        <v>100515</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15378,38 +15373,47 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>222771</v>
+        <v>223246</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628194.9184658813</v>
+        <v>627930.8491470228</v>
       </c>
       <c r="R124" t="n">
-        <v>6706067.122597958</v>
+        <v>6705804.092998104</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15421,7 +15425,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -15431,12 +15435,12 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
@@ -15446,7 +15450,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -15456,7 +15460,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>spridd i ung mycket rik lund</t>
+          <t>3 dm</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15483,10 +15487,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>67980564</v>
+        <v>67979969</v>
       </c>
       <c r="B125" t="n">
-        <v>101323</v>
+        <v>98431</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15499,16 +15503,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -15516,26 +15520,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628109.1512328837</v>
+        <v>628194.9184658813</v>
       </c>
       <c r="R125" t="n">
-        <v>6706157.854417819</v>
+        <v>6706067.122597958</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15562,7 +15557,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
@@ -15572,12 +15567,17 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2017-08-02</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>spridd i ung mycket rik lund</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15604,10 +15604,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>67980152</v>
+        <v>67980564</v>
       </c>
       <c r="B126" t="n">
-        <v>97655</v>
+        <v>101323</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15616,35 +15616,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>643</v>
+        <v>222395</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628169.8073260514</v>
+        <v>628109.1512328837</v>
       </c>
       <c r="R126" t="n">
-        <v>6706161.976738581</v>
+        <v>6706157.854417819</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2017-04-08</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2017-04-08</t>
+          <t>2017-08-02</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
@@ -15725,10 +15725,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>67980096</v>
+        <v>67980152</v>
       </c>
       <c r="B127" t="n">
-        <v>103088</v>
+        <v>97655</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15737,35 +15737,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221101</v>
+        <v>643</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pollich) Holub</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -15774,10 +15774,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628100.2027860719</v>
+        <v>628169.8073260514</v>
       </c>
       <c r="R127" t="n">
-        <v>6705893.98948249</v>
+        <v>6706161.976738581</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -15799,12 +15799,12 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2017-09-24</t>
+          <t>2017-04-08</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2017-09-24</t>
+          <t>2017-04-08</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
@@ -15846,10 +15846,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>68324624</v>
+        <v>67980096</v>
       </c>
       <c r="B128" t="n">
-        <v>98008</v>
+        <v>103088</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15858,44 +15858,50 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1256</v>
+        <v>221101</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Forselles</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Storön, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628258.1982261096</v>
+        <v>628100.2027860719</v>
       </c>
       <c r="R128" t="n">
-        <v>6706164.61557284</v>
+        <v>6705893.98948249</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15904,7 +15910,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -15914,12 +15920,12 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
@@ -15929,7 +15935,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
@@ -15949,22 +15955,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Sofia Lundell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>68324744</v>
+        <v>68324624</v>
       </c>
       <c r="B129" t="n">
-        <v>101323</v>
+        <v>98008</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15973,25 +15979,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222395</v>
+        <v>1256</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -16004,13 +16010,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628230.8992558946</v>
+        <v>628258.1982261096</v>
       </c>
       <c r="R129" t="n">
-        <v>6706098.009378131</v>
+        <v>6706164.61557284</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16076,10 +16082,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>68324786</v>
+        <v>68324744</v>
       </c>
       <c r="B130" t="n">
-        <v>97655</v>
+        <v>101323</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -16088,25 +16094,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>643</v>
+        <v>222395</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -16119,10 +16125,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628174.198298844</v>
+        <v>628230.8992558946</v>
       </c>
       <c r="R130" t="n">
-        <v>6706163.612846673</v>
+        <v>6706098.009378131</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16191,10 +16197,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>68324726</v>
+        <v>68324786</v>
       </c>
       <c r="B131" t="n">
-        <v>103346</v>
+        <v>97655</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16203,25 +16209,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221423</v>
+        <v>643</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Pollich) Holub</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -16234,10 +16240,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628261.3482242606</v>
+        <v>628174.198298844</v>
       </c>
       <c r="R131" t="n">
-        <v>6706145.479959488</v>
+        <v>6706163.612846673</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -16306,10 +16312,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>68324576</v>
+        <v>68324726</v>
       </c>
       <c r="B132" t="n">
-        <v>103088</v>
+        <v>103346</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16322,21 +16328,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221101</v>
+        <v>221423</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -16349,10 +16355,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628258.1982261096</v>
+        <v>628261.3482242606</v>
       </c>
       <c r="R132" t="n">
-        <v>6706164.61557284</v>
+        <v>6706145.479959488</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16421,10 +16427,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>69324427</v>
+        <v>68324576</v>
       </c>
       <c r="B133" t="n">
-        <v>97655</v>
+        <v>103088</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16433,25 +16439,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>643</v>
+        <v>221101</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -16460,17 +16466,17 @@
       <c r="L133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Skogen, Upl</t>
+          <t>Storön, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628171.8345359146</v>
+        <v>628258.1982261096</v>
       </c>
       <c r="R133" t="n">
-        <v>6706160.567999039</v>
+        <v>6706164.61557284</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16494,7 +16500,7 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
@@ -16504,7 +16510,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2017-08-20</t>
+          <t>2017-08-21</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
@@ -16524,22 +16530,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Sofia Lundell</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>75659828</v>
+        <v>69324427</v>
       </c>
       <c r="B134" t="n">
-        <v>43464</v>
+        <v>97655</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16548,43 +16554,41 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>101735</v>
+        <v>643</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Pollich) Holub</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Storön N om Båtfors NR, Upl</t>
+          <t>Skogen, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628321.0393427649</v>
+        <v>628171.8345359146</v>
       </c>
       <c r="R134" t="n">
-        <v>6706107.127517966</v>
+        <v>6706160.567999039</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -16611,7 +16615,7 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>1997-04-17</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
@@ -16621,7 +16625,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>1997-04-17</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
@@ -16629,11 +16633,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Gamla kläckhål i fnöskticka på döende björk.</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -16642,36 +16641,26 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>76897057</v>
+        <v>75659828</v>
       </c>
       <c r="B135" t="n">
-        <v>93295</v>
+        <v>43464</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16680,41 +16669,46 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>540</v>
+        <v>101735</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Barkkvastmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dicranum viride</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Sull. &amp; Lesq.) Lindb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
+          <t>Storön N om Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628083.8852646612</v>
+        <v>628321.0393427649</v>
       </c>
       <c r="R135" t="n">
-        <v>6705782.360603208</v>
+        <v>6706107.127517966</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16723,7 +16717,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -16733,12 +16727,12 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>1997-04-17</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
@@ -16748,7 +16742,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>1997-04-17</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
@@ -16758,7 +16752,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>EJ FUNNEN vid särskilt eftersök av arten! Eftersökt på flera lämpliga träd</t>
+          <t>Gamla kläckhål i fnöskticka på döende björk.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16770,42 +16764,35 @@
       <c r="AG135" t="b">
         <v>0</v>
       </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
-        </is>
-      </c>
-      <c r="AN135" t="n">
-        <v>0</v>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>0 substratenheter</t>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>81678646</v>
+        <v>76897057</v>
       </c>
       <c r="B136" t="n">
-        <v>103088</v>
+        <v>93295</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16814,41 +16801,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221101</v>
+        <v>540</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Barkkvastmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Dicranum viride</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sull. &amp; Lesq.) Lindb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Storön i S, Upl</t>
+          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>627915.8328835219</v>
+        <v>628083.8852646612</v>
       </c>
       <c r="R136" t="n">
-        <v>6706158.910743937</v>
+        <v>6705782.360603208</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16857,7 +16844,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -16867,12 +16854,12 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
@@ -16882,7 +16869,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
@@ -16892,7 +16879,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>EJ FUNNEN vid särskilt eftersök av arten! Eftersökt på flera lämpliga träd</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16903,26 +16890,43 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
+        </is>
+      </c>
+      <c r="AN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>0 substratenheter</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>81678836</v>
+        <v>81678646</v>
       </c>
       <c r="B137" t="n">
-        <v>103252</v>
+        <v>103088</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16935,43 +16939,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>224098</v>
+        <v>221101</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Storön i S, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628100.7969344617</v>
+        <v>627915.8328835219</v>
       </c>
       <c r="R137" t="n">
-        <v>6705974.952411474</v>
+        <v>6706158.910743937</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17014,6 +17009,11 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17040,10 +17040,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>88767204</v>
+        <v>81678836</v>
       </c>
       <c r="B138" t="n">
-        <v>98008</v>
+        <v>103252</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -17052,30 +17052,30 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1256</v>
+        <v>224098</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Forselles</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17085,14 +17085,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön i S, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628283.1850085423</v>
+        <v>628100.7969344617</v>
       </c>
       <c r="R138" t="n">
-        <v>6706115.162161387</v>
+        <v>6705974.952411474</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
@@ -17129,7 +17129,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2019-08-24</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
@@ -17161,10 +17161,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>88768762</v>
+        <v>81678808</v>
       </c>
       <c r="B139" t="n">
-        <v>81961</v>
+        <v>95511</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -17177,43 +17177,43 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1444</v>
+        <v>221944</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628252.0850752142</v>
+        <v>628979.0487636476</v>
       </c>
       <c r="R139" t="n">
-        <v>6706072.109707686</v>
+        <v>6706383.203949546</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
@@ -17282,10 +17282,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>92498748</v>
+        <v>88767204</v>
       </c>
       <c r="B140" t="n">
-        <v>78614</v>
+        <v>98008</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -17298,34 +17298,43 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229504</v>
+        <v>1256</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628083.902713461</v>
+        <v>628283.1850085423</v>
       </c>
       <c r="R140" t="n">
-        <v>6705781.867652238</v>
+        <v>6706115.162161387</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -17337,7 +17346,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -17347,12 +17356,12 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
@@ -17362,7 +17371,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
@@ -17378,36 +17387,26 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Lind, 50 cm</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>92499079</v>
+        <v>88768762</v>
       </c>
       <c r="B141" t="n">
-        <v>78569</v>
+        <v>81961</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -17416,38 +17415,47 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1444</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628083.902713461</v>
+        <v>628252.0850752142</v>
       </c>
       <c r="R141" t="n">
-        <v>6705781.867652238</v>
+        <v>6706072.109707686</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17459,7 +17467,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -17469,12 +17477,12 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
@@ -17484,7 +17492,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
@@ -17500,36 +17508,26 @@
       </c>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>Lönn, 20 cm</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>92498849</v>
+        <v>88767573</v>
       </c>
       <c r="B142" t="n">
-        <v>93148</v>
+        <v>95511</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17538,38 +17536,47 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1079</v>
+        <v>221944</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628083.902713461</v>
+        <v>627860.995006273</v>
       </c>
       <c r="R142" t="n">
-        <v>6705781.867652238</v>
+        <v>6706032.110850798</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17581,7 +17588,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -17591,12 +17598,12 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
@@ -17606,7 +17613,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
@@ -17622,36 +17629,26 @@
       </c>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>Lönn, 20 cm</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>54614051</v>
+        <v>92498748</v>
       </c>
       <c r="B143" t="n">
-        <v>101323</v>
+        <v>78614</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17660,46 +17657,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222395</v>
+        <v>229504</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Storön, N om Mellanön, Upl</t>
+          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628229.7720719024</v>
+        <v>628083.902713461</v>
       </c>
       <c r="R143" t="n">
-        <v>6706101.917646658</v>
+        <v>6705781.867652238</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17708,7 +17700,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -17718,32 +17710,27 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2015-07-28</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2015-07-28</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Källdrågspåverkad lövskog med inslag av granar. Växande på flera ställen, bl a här. Visad av upptäckaren Tommy Löfgren, Älvkarleby.</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17757,28 +17744,33 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>Källdrågspåverkad lövskog</t>
+          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Lind, 50 cm</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Karin Wiklund</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>54614084</v>
+        <v>92499079</v>
       </c>
       <c r="B144" t="n">
-        <v>93148</v>
+        <v>78569</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17787,46 +17779,41 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Storön, N om Mellanön, Upl</t>
+          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628190.9734412571</v>
+        <v>628083.902713461</v>
       </c>
       <c r="R144" t="n">
-        <v>6706080.80167107</v>
+        <v>6705781.867652238</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17835,7 +17822,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -17845,32 +17832,27 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2015-07-28</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2015-07-28</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Upptäckt av Karin Wiklund.</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17884,38 +17866,33 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>Källdrågspåverkad lövskog med inslag av granar.</t>
-        </is>
-      </c>
-      <c r="AL144" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior (ask)</t>
+          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior (ask)</t>
+          <t>Lönn, 20 cm</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Karin Wiklund</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>96882684</v>
+        <v>92498849</v>
       </c>
       <c r="B145" t="n">
-        <v>88953</v>
+        <v>93148</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17924,47 +17901,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5754</v>
+        <v>1079</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Ö väster om Mellanön södra, Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628051.3427417773</v>
+        <v>628083.902713461</v>
       </c>
       <c r="R145" t="n">
-        <v>6705807.861448036</v>
+        <v>6705781.867652238</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17991,7 +17959,7 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
@@ -18001,7 +17969,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
+          <t>2015-11-03</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -18017,30 +17985,36 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Översvämningspåverkad lövrik blandskog vid Nedre Dalälven</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Lönn, 20 cm</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96882682</v>
+        <v>54614051</v>
       </c>
       <c r="B146" t="n">
-        <v>88953</v>
+        <v>101323</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -18049,50 +18023,46 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5754</v>
+        <v>222395</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628191.0894720413</v>
+        <v>628229.7720719024</v>
       </c>
       <c r="R146" t="n">
-        <v>6706007.76271065</v>
+        <v>6706101.917646658</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -18116,22 +18086,27 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Källdrågspåverkad lövskog med inslag av granar. Växande på flera ställen, bl a här. Visad av upptäckaren Tommy Löfgren, Älvkarleby.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18142,30 +18117,31 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Källdrågspåverkad lövskog</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Joakim Ekman, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96882681</v>
+        <v>54614084</v>
       </c>
       <c r="B147" t="n">
-        <v>88953</v>
+        <v>93148</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -18174,50 +18150,46 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5754</v>
+        <v>1079</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, N om Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628181.4959590031</v>
+        <v>628190.9734412571</v>
       </c>
       <c r="R147" t="n">
-        <v>6706055.295816622</v>
+        <v>6706080.80167107</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -18241,22 +18213,27 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2015-07-28</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Upptäckt av Karin Wiklund.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18267,30 +18244,41 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Källdrågspåverkad lövskog med inslag av granar.</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior (ask)</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior (ask)</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Joakim Ekman, Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>96940711</v>
+        <v>96882684</v>
       </c>
       <c r="B148" t="n">
-        <v>101323</v>
+        <v>88953</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -18299,35 +18287,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>222395</v>
+        <v>5754</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -18336,10 +18324,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>627924.4350249297</v>
+        <v>628051.3427417773</v>
       </c>
       <c r="R148" t="n">
-        <v>6706153.292690015</v>
+        <v>6705807.861448036</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18351,7 +18339,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -18361,12 +18349,12 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
@@ -18376,7 +18364,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
@@ -18404,14 +18392,18 @@
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AY148" t="inlineStr"/>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>96940376</v>
+        <v>96882682</v>
       </c>
       <c r="B149" t="n">
-        <v>101680</v>
+        <v>88953</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -18420,35 +18412,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -18457,10 +18449,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628201.5719412938</v>
+        <v>628191.0894720413</v>
       </c>
       <c r="R149" t="n">
-        <v>6706032.810991442</v>
+        <v>6706007.76271065</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -18487,7 +18479,7 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
@@ -18497,17 +18489,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2021-04-25</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>lövrik översilningslund</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18530,14 +18517,18 @@
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AY149" t="inlineStr"/>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>96940496</v>
+        <v>96882681</v>
       </c>
       <c r="B150" t="n">
-        <v>103088</v>
+        <v>88953</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18546,35 +18537,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221101</v>
+        <v>5754</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -18583,10 +18574,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628214.0066003611</v>
+        <v>628181.4959590031</v>
       </c>
       <c r="R150" t="n">
-        <v>6706253.855520228</v>
+        <v>6706055.295816622</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18613,7 +18604,7 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
@@ -18623,7 +18614,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
@@ -18651,14 +18642,18 @@
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr"/>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>96940495</v>
+        <v>96940711</v>
       </c>
       <c r="B151" t="n">
-        <v>103088</v>
+        <v>101323</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18671,16 +18666,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221101</v>
+        <v>222395</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -18690,7 +18685,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -18704,10 +18699,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628112.5545650101</v>
+        <v>627924.4350249297</v>
       </c>
       <c r="R151" t="n">
-        <v>6706061.737648399</v>
+        <v>6706153.292690015</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18776,10 +18771,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>96940712</v>
+        <v>96940376</v>
       </c>
       <c r="B152" t="n">
-        <v>101323</v>
+        <v>101680</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18792,16 +18787,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>222395</v>
+        <v>222412</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -18811,12 +18806,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -18825,10 +18820,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628085.4430578864</v>
+        <v>628201.5719412938</v>
       </c>
       <c r="R152" t="n">
-        <v>6706129.377923595</v>
+        <v>6706032.810991442</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18855,7 +18850,7 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
@@ -18865,12 +18860,17 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>lövrik översilningslund</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18897,7 +18897,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>96940500</v>
+        <v>96940496</v>
       </c>
       <c r="B153" t="n">
         <v>103088</v>
@@ -18930,17 +18930,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>627942.4233098205</v>
+        <v>628214.0066003611</v>
       </c>
       <c r="R153" t="n">
-        <v>6706161.825010529</v>
+        <v>6706253.855520228</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18983,11 +18992,6 @@
       <c r="AB153" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -19014,10 +19018,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>96940713</v>
+        <v>96940495</v>
       </c>
       <c r="B154" t="n">
-        <v>101323</v>
+        <v>103088</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -19030,16 +19034,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222395</v>
+        <v>221101</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -19049,7 +19053,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -19063,10 +19067,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628047.1116747138</v>
+        <v>628112.5545650101</v>
       </c>
       <c r="R154" t="n">
-        <v>6706178.853476906</v>
+        <v>6706061.737648399</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -19135,10 +19139,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>98361442</v>
+        <v>96940712</v>
       </c>
       <c r="B155" t="n">
-        <v>103088</v>
+        <v>101323</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -19151,16 +19155,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221101</v>
+        <v>222395</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -19173,16 +19177,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Utvidgning av Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628263.7510153579</v>
+        <v>628085.4430578864</v>
       </c>
       <c r="R155" t="n">
-        <v>6706105.589691055</v>
+        <v>6706129.377923595</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -19209,7 +19218,7 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
@@ -19219,7 +19228,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
@@ -19239,26 +19248,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>98361440</v>
+        <v>96940500</v>
       </c>
       <c r="B156" t="n">
-        <v>100515</v>
+        <v>103088</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -19267,42 +19272,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>223246</v>
+        <v>221101</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Utvidgning av Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628254.8511656583</v>
+        <v>627942.4233098205</v>
       </c>
       <c r="R156" t="n">
-        <v>6706119.586444466</v>
+        <v>6706161.825010529</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -19329,7 +19330,7 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
@@ -19339,12 +19340,17 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19359,26 +19365,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>98362086</v>
+        <v>96940713</v>
       </c>
       <c r="B157" t="n">
-        <v>103346</v>
+        <v>101323</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -19391,21 +19393,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221423</v>
+        <v>222395</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -19413,16 +19415,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Utvidgning av Båtfors NR, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628458.5681011383</v>
+        <v>628047.1116747138</v>
       </c>
       <c r="R157" t="n">
-        <v>6706354.815500402</v>
+        <v>6706178.853476906</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -19449,7 +19456,7 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
@@ -19459,7 +19466,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
@@ -19479,26 +19486,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>98361439</v>
+        <v>98361442</v>
       </c>
       <c r="B158" t="n">
-        <v>98520</v>
+        <v>103088</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -19511,21 +19514,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222498</v>
+        <v>221101</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -19539,10 +19542,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628180.8687182952</v>
+        <v>628263.7510153579</v>
       </c>
       <c r="R158" t="n">
-        <v>6706282.291543726</v>
+        <v>6706105.589691055</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19615,10 +19618,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>98361438</v>
+        <v>98361440</v>
       </c>
       <c r="B159" t="n">
-        <v>101680</v>
+        <v>100515</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -19627,25 +19630,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>222412</v>
+        <v>223246</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -19659,10 +19662,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628184.0054905597</v>
+        <v>628254.8511656583</v>
       </c>
       <c r="R159" t="n">
-        <v>6706277.467658068</v>
+        <v>6706119.586444466</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19735,10 +19738,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>98361444</v>
+        <v>98362086</v>
       </c>
       <c r="B160" t="n">
-        <v>56859</v>
+        <v>103346</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19747,25 +19750,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103018</v>
+        <v>221423</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -19779,10 +19782,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628338.017946379</v>
+        <v>628458.5681011383</v>
       </c>
       <c r="R160" t="n">
-        <v>6706102.300922481</v>
+        <v>6706354.815500402</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19809,7 +19812,7 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
@@ -19819,7 +19822,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
@@ -19855,10 +19858,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>98361441</v>
+        <v>98361439</v>
       </c>
       <c r="B161" t="n">
-        <v>101680</v>
+        <v>98520</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19871,21 +19874,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -19899,10 +19902,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628261.7062640622</v>
+        <v>628180.8687182952</v>
       </c>
       <c r="R161" t="n">
-        <v>6706107.491310673</v>
+        <v>6706282.291543726</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19975,37 +19978,37 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>98361445</v>
+        <v>98361438</v>
       </c>
       <c r="B162" t="n">
-        <v>56632</v>
+        <v>101680</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103012</v>
+        <v>222412</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -20019,10 +20022,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628324.4555309615</v>
+        <v>628184.0054905597</v>
       </c>
       <c r="R162" t="n">
-        <v>6706150.185294815</v>
+        <v>6706277.467658068</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -20095,10 +20098,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>104729506</v>
+        <v>98361444</v>
       </c>
       <c r="B163" t="n">
-        <v>101323</v>
+        <v>56859</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -20107,47 +20110,42 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>222395</v>
+        <v>103018</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Storön i S, Upl</t>
+          <t>Utvidgning av Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628250.1671200242</v>
+        <v>628338.017946379</v>
       </c>
       <c r="R163" t="n">
-        <v>6706084.379980971</v>
+        <v>6706102.300922481</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -20174,7 +20172,7 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
@@ -20184,7 +20182,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
@@ -20204,22 +20202,26 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>104765687</v>
+        <v>98361441</v>
       </c>
       <c r="B164" t="n">
-        <v>88953</v>
+        <v>101680</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -20228,47 +20230,42 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5754</v>
+        <v>222412</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Storön i S, Upl</t>
+          <t>Utvidgning av Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628149.0472484285</v>
+        <v>628261.7062640622</v>
       </c>
       <c r="R164" t="n">
-        <v>6706092.148198992</v>
+        <v>6706107.491310673</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20295,7 +20292,7 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
@@ -20305,17 +20302,12 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>riklig runt i hela örtskogen</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -20330,26 +20322,30 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>56089985</v>
+        <v>98361445</v>
       </c>
       <c r="B165" t="n">
-        <v>55608</v>
+        <v>56632</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20358,39 +20354,38 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>102612</v>
+        <v>103012</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Storön, södra delen, Upl</t>
+          <t>Utvidgning av Båtfors NR, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>628117.9505775031</v>
+        <v>628324.4555309615</v>
       </c>
       <c r="R165" t="n">
-        <v>6706062.915777263</v>
+        <v>6706150.185294815</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20417,7 +20412,7 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2015-07-06</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
@@ -20427,17 +20422,12 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2015-07-06</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>hona med kull</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20452,22 +20442,26 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>113338984</v>
+        <v>104729506</v>
       </c>
       <c r="B166" t="n">
-        <v>103146</v>
+        <v>101323</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20480,16 +20474,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222412</v>
+        <v>222395</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -20499,24 +20493,24 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön i S, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>628085</v>
+        <v>628250.1671200242</v>
       </c>
       <c r="R166" t="n">
-        <v>6705932</v>
+        <v>6706084.379980971</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20528,7 +20522,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
@@ -20538,17 +20532,27 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2022-07-07</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20575,10 +20579,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>113338862</v>
+        <v>104765687</v>
       </c>
       <c r="B167" t="n">
-        <v>83043</v>
+        <v>88953</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20587,30 +20591,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1444</v>
+        <v>5754</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -20620,14 +20624,14 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön i S, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>628248</v>
+        <v>628149.0472484285</v>
       </c>
       <c r="R167" t="n">
-        <v>6706079</v>
+        <v>6706092.148198992</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20654,12 +20658,27 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
+          <t>2022-09-10</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>riklig runt i hela örtskogen</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20686,10 +20705,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>113353615</v>
+        <v>56089985</v>
       </c>
       <c r="B168" t="n">
-        <v>99363</v>
+        <v>55608</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20702,46 +20721,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1256</v>
+        <v>102612</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Forselles</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, södra delen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>628156</v>
+        <v>628117.9505775031</v>
       </c>
       <c r="R168" t="n">
-        <v>6705895</v>
+        <v>6706062.915777263</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20753,7 +20765,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
@@ -20763,17 +20775,32 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2015-07-06</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2015-07-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>hona med kull</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20782,7 +20809,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -20797,18 +20823,14 @@
           <t>Tommy Löfgren</t>
         </is>
       </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+      <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>115589805</v>
+        <v>113338984</v>
       </c>
       <c r="B169" t="n">
-        <v>56611</v>
+        <v>103146</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -20821,49 +20843,46 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100065</v>
+        <v>222412</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Båtsforstorpet - Mellanön, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>627928</v>
+        <v>628085</v>
       </c>
       <c r="R169" t="n">
-        <v>6705799</v>
+        <v>6705932</v>
       </c>
       <c r="S169" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20887,12 +20906,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20907,22 +20926,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>115581430</v>
+        <v>113338862</v>
       </c>
       <c r="B170" t="n">
-        <v>57792</v>
+        <v>83043</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -20935,49 +20954,46 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>102990</v>
+        <v>1444</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Båtsforstorpet - Mellanön, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>627928</v>
+        <v>628248</v>
       </c>
       <c r="R170" t="n">
-        <v>6705799</v>
+        <v>6706079</v>
       </c>
       <c r="S170" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20986,7 +21002,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
@@ -20996,17 +21012,17 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -21021,22 +21037,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>115581441</v>
+        <v>113353615</v>
       </c>
       <c r="B171" t="n">
-        <v>57680</v>
+        <v>99363</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -21049,45 +21065,49 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103001</v>
+        <v>1256</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Båtsforstorpet - Mellanön, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>627928</v>
+        <v>628156</v>
       </c>
       <c r="R171" t="n">
-        <v>6705799</v>
+        <v>6705895</v>
       </c>
       <c r="S171" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -21111,12 +21131,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21125,28 +21145,33 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
-        </is>
-      </c>
-      <c r="AY171" t="inlineStr"/>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121124754</v>
+        <v>115589805</v>
       </c>
       <c r="B172" t="n">
-        <v>105023</v>
+        <v>56611</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -21159,46 +21184,49 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>221101</v>
+        <v>100065</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Storön, Upl</t>
+          <t>Båtsforstorpet - Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>628078</v>
+        <v>627928</v>
       </c>
       <c r="R172" t="n">
-        <v>6706180</v>
+        <v>6705799</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21207,7 +21235,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
@@ -21217,22 +21245,17 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>fullt blommande !!</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21247,22 +21270,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121125136</v>
+        <v>115581430</v>
       </c>
       <c r="B173" t="n">
-        <v>83185</v>
+        <v>57792</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -21275,46 +21298,49 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1444</v>
+        <v>102990</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Storön i SV, Upl</t>
+          <t>Båtsforstorpet - Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>628202</v>
+        <v>627928</v>
       </c>
       <c r="R173" t="n">
-        <v>6706051</v>
+        <v>6705799</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21323,7 +21349,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
@@ -21333,17 +21359,17 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -21358,22 +21384,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121124862</v>
+        <v>115581441</v>
       </c>
       <c r="B174" t="n">
-        <v>103238</v>
+        <v>57680</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -21382,50 +21408,49 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>222395</v>
+        <v>103001</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Storön, Upl</t>
+          <t>Båtsforstorpet - Mellanön, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>628126</v>
+        <v>627928</v>
       </c>
       <c r="R174" t="n">
-        <v>6706055</v>
+        <v>6705799</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -21434,7 +21459,7 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="V174" t="inlineStr">
@@ -21444,17 +21469,17 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Älvkarleby</t>
+          <t>Tierp</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21469,22 +21494,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Oscar Nordahl</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121076904</v>
+        <v>121124754</v>
       </c>
       <c r="B175" t="n">
-        <v>57378</v>
+        <v>105023</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -21497,43 +21522,43 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100110</v>
+        <v>221101</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>628474</v>
+        <v>628078</v>
       </c>
       <c r="R175" t="n">
-        <v>6706309</v>
+        <v>6706180</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -21560,17 +21585,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>ropande</t>
+          <t>fullt blommande !!</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -21597,10 +21622,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122895461</v>
+        <v>121125136</v>
       </c>
       <c r="B176" t="n">
-        <v>94905</v>
+        <v>83185</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -21609,41 +21634,50 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1079</v>
+        <v>1444</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Fläskbacka, Fläskbacka, Upl</t>
+          <t>Storön i SV, Upl</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>628006</v>
+        <v>628202</v>
       </c>
       <c r="R176" t="n">
-        <v>6705651</v>
+        <v>6706051</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -21652,7 +21686,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -21662,27 +21696,17 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21697,22 +21721,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Andreas Öster, Cajsa Björkén</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122895471</v>
+        <v>121124862</v>
       </c>
       <c r="B177" t="n">
-        <v>82424</v>
+        <v>103238</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -21725,37 +21749,46 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>779</v>
+        <v>222395</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lindskål</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Holwaya mucida</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schulzer) Korf &amp; Abawi</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Fläskbacka, Fläskbacka, Upl</t>
+          <t>Storön, Upl</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>628006</v>
+        <v>628126</v>
       </c>
       <c r="R177" t="n">
-        <v>6705651</v>
+        <v>6706055</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -21764,7 +21797,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -21774,27 +21807,17 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -21809,22 +21832,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Andreas Öster, Cajsa Björkén</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122895467</v>
+        <v>121076904</v>
       </c>
       <c r="B178" t="n">
-        <v>79862</v>
+        <v>57378</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -21833,41 +21856,50 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Fläskbacka, Fläskbacka, Upl</t>
+          <t>Storön i söder, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628006</v>
+        <v>628474</v>
       </c>
       <c r="R178" t="n">
-        <v>6705651</v>
+        <v>6706309</v>
       </c>
       <c r="S178" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -21876,7 +21908,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
@@ -21886,27 +21918,22 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Tierp</t>
+          <t>Älvkarleby</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>ropande</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21921,22 +21948,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Andreas Öster, Cajsa Björkén</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122895427</v>
+        <v>122895461</v>
       </c>
       <c r="B179" t="n">
-        <v>79907</v>
+        <v>94905</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21945,25 +21972,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229504</v>
+        <v>1079</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -21973,10 +22000,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628085</v>
+        <v>628006</v>
       </c>
       <c r="R179" t="n">
-        <v>6705790</v>
+        <v>6705651</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -22045,37 +22072,37 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122895421</v>
+        <v>122895471</v>
       </c>
       <c r="B180" t="n">
-        <v>94913</v>
+        <v>82424</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1079</v>
+        <v>779</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lindskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Holwaya mucida</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schulzer) Korf &amp; Abawi</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -22085,10 +22112,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628079</v>
+        <v>628006</v>
       </c>
       <c r="R180" t="n">
-        <v>6705795</v>
+        <v>6705651</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -22154,6 +22181,342 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>122895467</v>
+      </c>
+      <c r="B181" t="n">
+        <v>79862</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>628006</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6705651</v>
+      </c>
+      <c r="S181" t="n">
+        <v>25</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>122895427</v>
+      </c>
+      <c r="B182" t="n">
+        <v>79907</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>628085</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6705790</v>
+      </c>
+      <c r="S182" t="n">
+        <v>25</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>122895421</v>
+      </c>
+      <c r="B183" t="n">
+        <v>94913</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Neckera pennata</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Fläskbacka, Fläskbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>628079</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6705795</v>
+      </c>
+      <c r="S183" t="n">
+        <v>25</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58719-2024 artfynd.xlsx
+++ b/artfynd/A 58719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY262"/>
+  <dimension ref="A1:AZ262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091696</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115589805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115581430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115581441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361451</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115589797</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090706</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090714</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091601</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091095</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2255,6 +2330,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980303</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361450</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2462,6 +2547,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767573</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999783</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2670,6 +2765,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940711</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2781,6 +2881,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090497</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980245</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2999,6 +3109,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92497801</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99664325</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3208,6 +3328,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498429</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895320</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3423,6 +3553,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67251433</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3546,6 +3681,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67258346</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3652,6 +3792,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091479</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3763,6 +3908,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091480</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3869,6 +4019,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124656</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3980,6 +4135,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000716</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4090,6 +4250,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220750</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4196,6 +4361,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980152</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4307,6 +4477,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980182</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4407,6 +4582,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68324786</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4507,6 +4687,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69324427</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4621,6 +4806,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113353616</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4728,6 +4918,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895471</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4860,6 +5055,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614084</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4971,6 +5171,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090294</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5082,6 +5287,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090297</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5193,6 +5403,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090299</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5304,6 +5519,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090307</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5414,6 +5634,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88848845</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5521,6 +5746,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498849</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5628,6 +5858,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498850</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5735,6 +5970,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895421</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5842,6 +6082,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895461</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5964,6 +6209,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614058</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6070,6 +6320,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091631</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6181,6 +6436,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091634</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6287,6 +6547,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091635</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6389,6 +6654,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091646</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6491,6 +6761,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091647</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6593,6 +6868,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091648</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6699,6 +6979,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091652</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6805,6 +7090,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091654</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6911,6 +7201,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091655</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7017,6 +7312,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091656</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7123,6 +7423,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091657</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7229,6 +7534,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091659</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7340,6 +7650,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091660</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7442,6 +7757,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091661</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7548,6 +7868,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091663</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7654,6 +7979,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091664</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7760,6 +8090,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091665</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7866,6 +8201,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091666</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7977,6 +8317,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091669</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8088,6 +8433,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091670</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8194,6 +8544,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091671</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8305,6 +8660,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091673</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8411,6 +8771,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091674</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8517,6 +8882,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091676</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8628,6 +8998,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091690</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8734,6 +9109,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091691</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8840,6 +9220,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091693</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8951,6 +9336,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9057,6 +9447,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091695</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9159,6 +9554,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091702</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9265,6 +9665,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091703</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9376,6 +9781,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091704</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9482,6 +9892,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091706</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9588,6 +10003,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091708</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9694,6 +10114,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091709</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9796,6 +10221,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091710</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9898,6 +10328,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091711</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10004,6 +10439,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000850</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10110,6 +10550,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000859</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10216,6 +10661,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000860</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10326,6 +10776,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219760</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10428,6 +10883,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980085</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10530,6 +10990,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980086</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10630,6 +11095,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68324624</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10736,6 +11206,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767204</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10850,6 +11325,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113353615</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10956,6 +11436,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88768762</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11062,6 +11547,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338862</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11168,6 +11658,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125136</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11292,6 +11787,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220331</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11398,6 +11898,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62001969</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11500,6 +12005,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091751</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11607,6 +12117,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895350</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11714,6 +12229,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895352</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11816,6 +12336,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62515078</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11918,6 +12443,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980995</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12028,6 +12558,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96882681</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12138,6 +12673,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96882682</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12248,6 +12788,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96882684</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12359,6 +12904,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104765687</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12466,6 +13016,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92499078</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12578,6 +13133,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92499080</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12698,6 +13258,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99664323</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12805,6 +13370,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895467</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12916,6 +13486,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113339158</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13027,6 +13602,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121076904</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13144,6 +13724,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75659828</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13251,6 +13836,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56089985</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13356,6 +13946,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361445</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13461,6 +14056,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361466</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13566,6 +14166,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361444</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13675,6 +14280,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64526644</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13781,6 +14391,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091979</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13907,6 +14522,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614061</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14013,6 +14633,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940695</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14135,6 +14760,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614052</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14237,6 +14867,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090670</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14339,6 +14974,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090672</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14441,6 +15081,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090673</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14543,6 +15188,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090675</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14645,6 +15295,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090678</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14747,6 +15402,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090688</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14849,6 +15509,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090696</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14951,6 +15616,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090707</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15053,6 +15723,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090712</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15155,6 +15830,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090713</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15266,6 +15946,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090715</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15368,6 +16053,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090716</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15470,6 +16160,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090717</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15572,6 +16267,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090718</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15674,6 +16374,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090719</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15776,6 +16481,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090724</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15878,6 +16588,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090731</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15984,6 +16699,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090732</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16086,6 +16806,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090734</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16188,6 +16913,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090736</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16290,6 +17020,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090737</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16392,6 +17127,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090738</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16494,6 +17234,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090739</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16600,6 +17345,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090745</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16702,6 +17452,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090753</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16804,6 +17559,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124084</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16906,6 +17666,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999966</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17008,6 +17773,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999968</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17118,6 +17888,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219755</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17220,6 +17995,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980458</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17322,6 +18102,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980459</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17424,6 +18209,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767702</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17529,6 +18319,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361443</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17631,6 +18426,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090425</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17733,6 +18533,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090430</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17835,6 +18640,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090439</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17937,6 +18747,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090441</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18039,6 +18854,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999666</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18149,6 +18969,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219708</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18271,6 +19096,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614050</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18393,6 +19223,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614059</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18499,6 +19334,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091597</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18601,6 +19441,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091599</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18703,6 +19548,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091600</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18805,6 +19655,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091602</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18907,6 +19762,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091603</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19018,6 +19878,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091604</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19124,6 +19989,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091607</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19230,6 +20100,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091608</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19336,6 +20211,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000778</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19450,6 +20330,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219701</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19556,6 +20441,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980096</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19662,6 +20552,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980098</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19768,6 +20663,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980100</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19874,6 +20774,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980101</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19974,6 +20879,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68324576</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20080,6 +20990,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940495</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20186,6 +21101,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940496</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20292,6 +21212,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940498</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20397,6 +21322,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361442</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20503,6 +21433,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729246</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20614,6 +21549,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124754</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20736,6 +21676,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614054</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20838,6 +21783,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091096</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20944,6 +21894,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091098</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21046,6 +22001,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091099</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21148,6 +22108,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091100</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21245,6 +22210,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091101</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21347,6 +22317,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091111</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21453,6 +22428,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091112</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21559,6 +22539,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091126</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21661,6 +22646,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091129</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21767,6 +22757,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124449</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21873,6 +22868,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124480</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21977,6 +22977,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61228368</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22083,6 +23088,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000529</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22185,6 +23195,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000539</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22287,6 +23302,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000540</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22397,6 +23417,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219785</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22497,6 +23522,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68324726</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22602,6 +23632,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361446</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22707,6 +23742,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98362086</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22809,6 +23849,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000395</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22911,6 +23956,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678808</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23013,6 +24063,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767569</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23135,6 +24190,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614053</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23237,6 +24297,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091920</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23347,6 +24412,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220286</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23469,6 +24539,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54614051</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23575,6 +24650,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090580</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23681,6 +24761,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090581</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23787,6 +24872,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090585</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23893,6 +24983,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090590</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23999,6 +25094,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090591</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24101,6 +25201,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090595</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24207,6 +25312,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090600</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24313,6 +25423,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090602</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24419,6 +25534,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090603</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24525,6 +25645,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090604</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24631,6 +25756,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090605</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24737,6 +25867,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999781</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24847,6 +25982,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220241</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24953,6 +26093,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980562</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25059,6 +26204,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980564</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25159,6 +26309,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68324744</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25265,6 +26420,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940712</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25371,6 +26531,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940713</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25477,6 +26642,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729506</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25583,6 +26753,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124862</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25689,6 +26864,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091805</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25795,6 +26975,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091809</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25901,6 +27086,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091812</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26012,6 +27202,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091831</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26123,6 +27318,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091849</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26229,6 +27429,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000995</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26339,6 +27544,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67219748</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26445,6 +27655,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767077</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26551,6 +27766,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767113</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26657,6 +27877,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940308</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26768,6 +27993,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940376</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26873,6 +28103,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361438</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26978,6 +28213,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361441</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27084,6 +28324,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338984</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27190,6 +28435,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338988</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27300,6 +28550,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220682</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27405,6 +28660,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361439</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27519,6 +28779,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220271</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27631,6 +28896,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67235984</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27733,6 +29003,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67979969</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27844,6 +29119,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980038</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27954,6 +29234,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67220689</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28059,6 +29344,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98361440</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28165,6 +29455,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678836</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28272,6 +29567,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498748</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28379,6 +29679,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122895427</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28497,8 +29802,276 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67261281</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>